--- a/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit pas. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter. Nine dit : ce n'est pas gentil. Elle ramasse le cartable. Elle le tend. Le soir, maman vient. Nine raconte. Maman dit : tu as bien fait. Pas rire. Pas répéter. On dit : ce n'est pas gentil.</t>
+          <t>Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit pas. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Elle ramasse le cartable. Elle le tend. Le soir, maman vient. Nine raconte. Tu as bien fait. Pas rire. Pas répéter. Ce n'est pas gentil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit pas. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter.
+enfant-f|Ce n'est pas gentil. Elle ramasse le cartable. Elle le tend.
+narrateur|Le soir, maman vient. Nine raconte.
+maman|Tu as bien fait. Pas rire. Pas répéter.
+narrateur|Ce n'est pas gentil.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1471,6 +1496,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade rit. Que fait Nine ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1495,7 +1525,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nine n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil.</t>
+          <t>Nine n'a pas ri. Elle n'a pas répété. Elle Ce n'est pas gentil.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1637,6 +1667,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nine n'a pas ri. Elle n'a pas répété. Elle
+enfant-f|Ce n'est pas gentil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend la main de Nine. Ils marchent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ce n'est pas gentil.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Un camarade rit. Que fait Nine ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
 enfant-f|Ce n'est pas gentil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Maman prend la main de Nine. Ils marchent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nine ne rit pas du cartable</t>
+          <t>Le cartable dans le couloir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dans le couloir qui résonne, le cartable d'Amir tombe. Sarah ramasse, tend, dit que ce n'est pas gentil. Le soir, elle raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit pas. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Elle ramasse le cartable. Elle le tend. Le soir, maman vient. Nine raconte. Tu as bien fait. Pas rire. Pas répéter. Ce n'est pas gentil.</t>
+          <t>Le couloir de l'école résonne, tout creux. Une fermeture éclair chante, loin. Les casiers en bois sentent la pomme du goûter. Un pas tapote, puis s'arrête. Ton cartable est un peu lourd, Sarah. Tu l'as entendu, le couloir ? Oui, maman. Il fait un écho. On pose le sac près du casier. Tout doux. D'accord. Je reviens te chercher. On aura du cacao. Oui. En ce moment, Sarah pose son cartable. Le zip est froid sous les doigts. Amir arrive avec le sien. Le cartable glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Sarah n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Amir. Elle ramasse le cartable. Le tissu est rêche, un peu lourd. Elle le tend. Merci, Sarah. Amir reprend le cartable. Il le pose droit, près du bois. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Le couloir est plus calme. Ça sent encore la pomme. Un casier claque, tout loin, puis plus. Te voilà, Sarah. Tu me racontes le cartable ? Le cartable d'Amir est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. C'est du bon travail. Tu as fini ta pomme, ce midi ? Oui, maman. Le cacao t'attend à la maison. Sarah prend la main de maman. L'écho du couloir s'est tu. Il reste le bois des casiers, tout calme. On marche tout doux ? Oui, maman. Leurs pas tapotent le plancher. La fermeture éclair ne chante plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit pas. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter.
-enfant-f|Ce n'est pas gentil. Elle ramasse le cartable. Elle le tend.
-narrateur|Le soir, maman vient. Nine raconte.
-maman|Tu as bien fait. Pas rire. Pas répéter.
-narrateur|Ce n'est pas gentil.</t>
+          <t>narrateur|Le couloir de l'école résonne, tout creux.
+narrateur|Une fermeture éclair chante, loin.
+narrateur|Les casiers en bois sentent la pomme du goûter.
+narrateur|Un pas tapote, puis s'arrête.
+maman|Ton cartable est un peu lourd, Sarah.
+maman|Tu l'as entendu, le couloir ?
+enfant-f|Oui, maman.
+enfant-f|Il fait un écho.
+maman|On pose le sac près du casier.
+maman|Tout doux.
+enfant-f|D'accord.
+maman|Je reviens te chercher.
+maman|On aura du cacao.
+enfant-f|Oui.
+narrateur|En ce moment, Sarah pose son cartable.
+narrateur|Le zip est froid sous les doigts.
+narrateur|Amir arrive avec le sien.
+narrateur|Le cartable glisse.
+narrateur|Il tombe près du casier.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Sarah n'est pas là pour rire.
+narrateur|Elle ne répète pas.
+enfant-f|Ce n'est pas gentil.
+narrateur|Elle va vers Amir.
+narrateur|Elle ramasse le cartable.
+narrateur|Le tissu est rêche, un peu lourd.
+narrateur|Elle le tend.
+copain|Merci, Sarah.
+narrateur|Amir reprend le cartable.
+narrateur|Il le pose droit, près du bois.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-f|On aide.
+narrateur|Le soir, maman pousse la porte.
+narrateur|Le couloir est plus calme.
+narrateur|Ça sent encore la pomme.
+narrateur|Un casier claque, tout loin, puis plus.
+maman|Te voilà, Sarah.
+maman|Tu me racontes le cartable ?
+enfant-f|Le cartable d'Amir est tombé.
+enfant-f|J'ai ramassé.
+enfant-f|J'ai tendu.
+enfant-f|Ce n'est pas gentil, de rire.
+maman|Tu as bien fait.
+maman|Il ne faut pas rire.
+maman|Il ne faut pas répéter.
+maman|On va vers l'ami.
+maman|On aide.
+maman|C'est du bon travail.
+maman|Tu as fini ta pomme, ce midi ?
+enfant-f|Oui, maman.
+maman|Le cacao t'attend à la maison.
+narrateur|Sarah prend la main de maman.
+narrateur|L'écho du couloir s'est tu.
+narrateur|Il reste le bois des casiers, tout calme.
+maman|On marche tout doux ?
+enfant-f|Oui, maman.
+narrateur|Leurs pas tapotent le plancher.
+narrateur|La fermeture éclair ne chante plus.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade rit. Que fait Nine ?</t>
+          <t>Un camarade rit. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade rit. Que fait Nine ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nine n'a pas ri. Elle n'a pas répété. Elle Ce n'est pas gentil.</t>
+          <t>Sarah n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le cartable. Bravo, Sarah. C'est du bon travail. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Amir. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,8 +1746,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nine n'a pas ri. Elle n'a pas répété. Elle
-enfant-f|Ce n'est pas gentil.</t>
+          <t>narrateur|Sarah n'a pas ri.
+narrateur|Elle n'a pas répété.
+narrateur|Elle a dit : ce n'est pas gentil.
+narrateur|Elle a ramassé le cartable.
+maman|Bravo, Sarah.
+maman|C'est du bon travail.
+maman|On n'est pas là pour rire.
+maman|On n'est pas là pour répéter.
+enfant-f|J'ai aidé Amir.
+maman|Oui.
+maman|Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend la main de Nine. Ils marchent.</t>
+          <t>Maman prend la main de Sarah. Ils marchent. Le cacao va être chaud. Tu as les épaules légères, maintenant ? Oui, maman. Le zip du cartable d'Amir est fermé. Le couloir ne résonne plus. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,7 +1924,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend la main de Nine. Ils marchent.</t>
+          <t>narrateur|Maman prend la main de Sarah.
+narrateur|Ils marchent.
+maman|Le cacao va être chaud.
+maman|Tu as les épaules légères, maintenant ?
+enfant-f|Oui, maman.
+narrateur|Le zip du cartable d'Amir est fermé.
+narrateur|Le couloir ne résonne plus.
+maman|On rentre ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1873,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé le cartable. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. La pomme du goûter n'est plus qu'une odeur. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai ramassé le cartable.
+enfant-f|Ce n'est pas gentil, de rire.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La pomme du goûter n'est plus qu'une odeur.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2035,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le couloir de l'école résonne, tout creux. Une fermeture éclair chante, loin. Les casiers en bois sentent la pomme du goûter. Un pas tapote, puis s'arrête. Ton cartable est un peu lourd, Sarah. Tu l'as entendu, le couloir ? Oui, maman. Il fait un écho. On pose le sac près du casier. Tout doux. D'accord. Je reviens te chercher. On aura du cacao. Oui. En ce moment, Sarah pose son cartable. Le zip est froid sous les doigts. Amir arrive avec le sien. Le cartable glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Sarah n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Amir. Elle ramasse le cartable. Le tissu est rêche, un peu lourd. Elle le tend. Merci, Sarah. Amir reprend le cartable. Il le pose droit, près du bois. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Le couloir est plus calme. Ça sent encore la pomme. Un casier claque, tout loin, puis plus. Te voilà, Sarah. Tu me racontes le cartable ? Le cartable d'Amir est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. C'est du bon travail. Tu as fini ta pomme, ce midi ? Oui, maman. Le cacao t'attend à la maison. Sarah prend la main de maman. L'écho du couloir s'est tu. Il reste le bois des casiers, tout calme. On marche tout doux ? Oui, maman. Leurs pas tapotent le plancher. La fermeture éclair ne chante plus.</t>
+          <t>Le couloir de l'école résonne, tout creux. Une fermeture éclair chante, loin. Les casiers en bois sentent la pomme du goûter. Un pas tapote, puis s'arrête. Ton cartable est un peu lourd, Sarah. Tu l'as entendu, le couloir ? Oui, maman. Il fait un écho. On pose le sac près du casier. Tout doux. D'accord. Je reviens te chercher. On aura du cacao. Oui. En ce moment, Sarah pose son cartable. Le zip est froid sous les doigts. Amir arrive avec le sien. Le cartable glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Sarah n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Amir. Elle ramasse le cartable. Le tissu est rêche, un peu lourd. Elle le tend. Merci, Sarah. Amir reprend le cartable. Il le pose droit, près du bois. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Le couloir est plus calme. Ça sent encore la pomme. Un casier claque, tout loin, puis plus. Te voilà, Sarah. Tu me racontes le cartable ? Le cartable d'Amir est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. Tu as fini ta pomme, ce midi ? Oui, maman. Le cacao t'attend à la maison. Sarah prend la main de maman. L'écho du couloir s'est tu. Il reste le bois des casiers, tout calme. On marche tout doux ? Oui, maman. Leurs pas tapotent le plancher. La fermeture éclair ne chante plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nine est à l'école. Blaise fait tomber son cartable. Un camarade commence à rire. Nine ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Nine ne répète pas. Il ne faut pas répéter. Nine dit : ce n'est pas gentil. Elle ramasse le cartable. Elle le tend. Le soir, maman vient. Nine raconte. Maman dit : tu as bien fait. Pas rire. Pas répéter. On dit : ce n'est pas gentil.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le couloir de l'école résonne, tout creux. Une fermeture éclair chante, loin. Les casiers en bois sentent la pomme du goûter. Un pas tapote, puis s'arrête. Ton cartable est un peu lourd, Sarah. Tu l'as entendu, le couloir ? Oui, maman. Il fait un écho. On pose le sac près du casier. Tout doux. D'accord. Je reviens te chercher. On aura du cacao. Oui. En ce moment, Sarah pose son cartable. Le zip est froid sous les doigts. Amir arrive avec le sien. Le cartable glisse. Il tombe près du casier. Un camarade commence un petit rire. Le rire est court. Sarah n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Amir. Elle ramasse le cartable. Le tissu est rêche, un peu lourd. Elle le tend. Merci, Sarah. Amir reprend le cartable. Il le pose droit, près du bois. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Le couloir est plus calme. Ça sent encore la pomme. Un casier claque, tout loin, puis plus. Te voilà, Sarah. Tu me racontes le cartable ? Le cartable d'Amir est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. Tu as fini ta pomme, ce midi ? Oui, maman. Le cacao t'attend à la maison. Sarah prend la main de maman. L'écho du couloir s'est tu. Il reste le bois des casiers, tout calme. On marche tout doux ? Oui, maman. Leurs pas tapotent le plancher. La fermeture éclair ne chante plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1375,7 +1375,6 @@
 maman|Il ne faut pas répéter.
 maman|On va vers l'ami.
 maman|On aide.
-maman|C'est du bon travail.
 maman|Tu as fini ta pomme, ce midi ?
 enfant-f|Oui, maman.
 maman|Le cacao t'attend à la maison.
@@ -1388,7 +1387,6 @@
 narrateur|La fermeture éclair ne chante plus.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1418,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade rit. Que fait Ni&lt;emphasis level="moderate"&gt;ne&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le cartable. Bravo, Sarah. C'est du bon travail. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Amir. Oui. Tu es allée vers lui.</t>
+          <t>Sarah n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le cartable. Bravo, Sarah. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Amir. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nine n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le cartable. Bravo, Sarah. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Amir. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1748,6 @@
 narrateur|Elle a dit : ce n'est pas gentil.
 narrateur|Elle a ramassé le cartable.
 maman|Bravo, Sarah.
-maman|C'est du bon travail.
 maman|On n'est pas là pour rire.
 maman|On n'est pas là pour répéter.
 enfant-f|J'ai aidé Amir.
@@ -1759,7 +1755,6 @@
 maman|Tu es allée vers lui.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prend la main de Ni&lt;emphasis level="moderate"&gt;ne&lt;/emphasis&gt;. Ils marchent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman prend la main de Sarah. Ils marchent. Le cacao va être chaud. Tu as les épaules légères, maintenant ? Oui, maman. Le zip du cartable d'Amir est fermé. Le couloir ne résonne plus. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1930,6 @@
 enfant-f|Oui.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé le cartable. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. La pomme du goûter n'est plus qu'une odeur. L'histoire est finie.</t>
+          <t>J'ai ramassé le cartable. Ce n'est pas gentil, de rire. Bravo. La pomme du goûter n'est plus qu'une odeur.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé le cartable. Ce n'est pas gentil, de rire. Bravo. La pomme du goûter n'est plus qu'une odeur.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2097,9 @@
           <t>enfant-f|J'ai ramassé le cartable.
 enfant-f|Ce n'est pas gentil, de rire.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La pomme du goûter n'est plus qu'une odeur.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La pomme du goûter n'est plus qu'une odeur.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nine, Blaise, maman</t>
+          <t>Sarah, Amir, maman</t>
         </is>
       </c>
     </row>
